--- a/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Revenue.xlsx
@@ -88,12 +88,12 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T105</t>
   </si>
   <si>
-    <t>T100</t>
-  </si>
-  <si>
     <t>department</t>
   </si>
   <si>
@@ -124,7 +124,7 @@
     <t>D5201</t>
   </si>
   <si>
-    <t xml:space="preserve">D5202                    </t>
+    <t>D5202</t>
   </si>
   <si>
     <t xml:space="preserve">D5205                    </t>
@@ -593,7 +593,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="2">
-        <v>53234.7200</v>
+        <v>2831193.4700</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -607,7 +607,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="2">
-        <v>2831193.4700</v>
+        <v>53234.7200</v>
       </c>
     </row>
     <row r="7" spans="1:4">
